--- a/phase2/june2026/RQ2-probes.xlsx
+++ b/phase2/june2026/RQ2-probes.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darren.gemoets_cn\Documents\ITM\git\itm-ingest\phase2\june2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A73C18F-02A8-48E6-AE7D-91A6F22C2E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5C3078-4E97-484D-BB36-A4609974939C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{33EED27A-9AE1-4BDD-B317-916B923F03F2}"/>
   </bookViews>
   <sheets>
     <sheet name="AF" sheetId="1" r:id="rId1"/>
-    <sheet name="SS" sheetId="3" r:id="rId2"/>
-    <sheet name="PS" sheetId="4" r:id="rId3"/>
+    <sheet name="MF" sheetId="6" r:id="rId2"/>
+    <sheet name="SS" sheetId="3" r:id="rId3"/>
+    <sheet name="PS" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AF!$A$1:$E$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">PS!$A$1:$E$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SS!$A$1:$E$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MF!$A$1:$E$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">PS!$A$1:$E$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SS!$A$1:$E$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="280">
   <si>
     <t>probe_id</t>
   </si>
@@ -610,6 +612,276 @@
   </si>
   <si>
     <t>June2026-PS-eval.Probe 5238</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2114</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2115</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2116</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2117</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2118</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2119</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2120</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2121</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2122</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2123</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2124</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2125</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2126</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2127</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2128</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2129</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2130</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2131</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2132</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2133</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2134</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2135</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2136</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2137</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2138</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2139</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2140</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2141</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2142</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2143</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2144</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2145</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2146</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2147</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2148</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2149</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2150</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2151</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2152</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2153</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2154</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2155</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2156</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2157</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2158</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2159</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2160</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2161</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2162</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2163</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2164</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2165</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2166</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2167</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2168</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2169</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2170</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2171</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2172</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2173</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2174</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2175</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2176</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2177</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2178</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2179</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2180</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2181</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2182</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2183</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2184</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2185</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2186</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2187</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2188</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2189</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2190</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2191</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2192</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2193</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2194</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2195</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2196</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2197</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2198</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2199</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2200</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2201</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2202</t>
+  </si>
+  <si>
+    <t>Jun2026-MF-eval.Probe 2203</t>
   </si>
 </sst>
 </file>
@@ -3033,6 +3305,1570 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF963FB-848F-441E-8C2F-7C313605947B}">
+  <dimension ref="A1:E91"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C2">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D2">
+        <v>0.96657080399999995</v>
+      </c>
+      <c r="E2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C3">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D3">
+        <v>0.92956650399999996</v>
+      </c>
+      <c r="E3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C4">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D4">
+        <v>0.63015454500000001</v>
+      </c>
+      <c r="E4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C5">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D5">
+        <v>0.57584163399999999</v>
+      </c>
+      <c r="E5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="C6">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D6">
+        <v>0.39252177599999999</v>
+      </c>
+      <c r="E6">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C7">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D7">
+        <v>0.57404902800000002</v>
+      </c>
+      <c r="E7">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C8">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D8">
+        <v>0.53704472800000003</v>
+      </c>
+      <c r="E8">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C9">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D9">
+        <v>0.23763276899999999</v>
+      </c>
+      <c r="E9">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C10">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D10">
+        <v>0.183319858</v>
+      </c>
+      <c r="E10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C11">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D11">
+        <v>0.39072917000000001</v>
+      </c>
+      <c r="E11">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B12">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C12">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D12">
+        <v>0.35372487000000002</v>
+      </c>
+      <c r="E12">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>201</v>
+      </c>
+      <c r="B13">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C13">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D13">
+        <v>5.4312910999999998E-2</v>
+      </c>
+      <c r="E13">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B14">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C14">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D14">
+        <v>0.336416259</v>
+      </c>
+      <c r="E14">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>203</v>
+      </c>
+      <c r="B15">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C15">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D15">
+        <v>0.29941195900000001</v>
+      </c>
+      <c r="E15">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B16">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C16">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="D16">
+        <v>3.7004299999999997E-2</v>
+      </c>
+      <c r="E16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C17">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D17">
+        <v>0.96657080399999995</v>
+      </c>
+      <c r="E17">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C18">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D18">
+        <v>0.92956650399999996</v>
+      </c>
+      <c r="E18">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B19">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C19">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D19">
+        <v>0.63015454500000001</v>
+      </c>
+      <c r="E19">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>208</v>
+      </c>
+      <c r="B20">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C20">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D20">
+        <v>0.57584163399999999</v>
+      </c>
+      <c r="E20">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B21">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="C21">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D21">
+        <v>0.39252177599999999</v>
+      </c>
+      <c r="E21">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>210</v>
+      </c>
+      <c r="B22">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C22">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D22">
+        <v>0.57404902800000002</v>
+      </c>
+      <c r="E22">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>211</v>
+      </c>
+      <c r="B23">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C23">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D23">
+        <v>0.53704472800000003</v>
+      </c>
+      <c r="E23">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>212</v>
+      </c>
+      <c r="B24">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C24">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D24">
+        <v>0.23763276899999999</v>
+      </c>
+      <c r="E24">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>213</v>
+      </c>
+      <c r="B25">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C25">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D25">
+        <v>0.183319858</v>
+      </c>
+      <c r="E25">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>214</v>
+      </c>
+      <c r="B26">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C26">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D26">
+        <v>0.39072917000000001</v>
+      </c>
+      <c r="E26">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C27">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D27">
+        <v>0.35372487000000002</v>
+      </c>
+      <c r="E27">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>216</v>
+      </c>
+      <c r="B28">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C28">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D28">
+        <v>5.4312910999999998E-2</v>
+      </c>
+      <c r="E28">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>217</v>
+      </c>
+      <c r="B29">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C29">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D29">
+        <v>0.336416259</v>
+      </c>
+      <c r="E29">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>218</v>
+      </c>
+      <c r="B30">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C30">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D30">
+        <v>0.29941195900000001</v>
+      </c>
+      <c r="E30">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C31">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="D31">
+        <v>3.7004299999999997E-2</v>
+      </c>
+      <c r="E31">
+        <v>0.17100000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>220</v>
+      </c>
+      <c r="B32">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C32">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D32">
+        <v>0.96657080399999995</v>
+      </c>
+      <c r="E32">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>221</v>
+      </c>
+      <c r="B33">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C33">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D33">
+        <v>0.92956650399999996</v>
+      </c>
+      <c r="E33">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>222</v>
+      </c>
+      <c r="B34">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C34">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D34">
+        <v>0.63015454500000001</v>
+      </c>
+      <c r="E34">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C35">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D35">
+        <v>0.57584163399999999</v>
+      </c>
+      <c r="E35">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B36">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="C36">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D36">
+        <v>0.39252177599999999</v>
+      </c>
+      <c r="E36">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>225</v>
+      </c>
+      <c r="B37">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C37">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D37">
+        <v>0.57404902800000002</v>
+      </c>
+      <c r="E37">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>226</v>
+      </c>
+      <c r="B38">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C38">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D38">
+        <v>0.53704472800000003</v>
+      </c>
+      <c r="E38">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>227</v>
+      </c>
+      <c r="B39">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C39">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D39">
+        <v>0.23763276899999999</v>
+      </c>
+      <c r="E39">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>228</v>
+      </c>
+      <c r="B40">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C40">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D40">
+        <v>0.183319858</v>
+      </c>
+      <c r="E40">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>229</v>
+      </c>
+      <c r="B41">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C41">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D41">
+        <v>0.39072917000000001</v>
+      </c>
+      <c r="E41">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>230</v>
+      </c>
+      <c r="B42">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C42">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D42">
+        <v>0.35372487000000002</v>
+      </c>
+      <c r="E42">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>231</v>
+      </c>
+      <c r="B43">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C43">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D43">
+        <v>5.4312910999999998E-2</v>
+      </c>
+      <c r="E43">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>232</v>
+      </c>
+      <c r="B44">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C44">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D44">
+        <v>0.336416259</v>
+      </c>
+      <c r="E44">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>233</v>
+      </c>
+      <c r="B45">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C45">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D45">
+        <v>0.29941195900000001</v>
+      </c>
+      <c r="E45">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>234</v>
+      </c>
+      <c r="B46">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C46">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="D46">
+        <v>3.7004299999999997E-2</v>
+      </c>
+      <c r="E46">
+        <v>0.32950000000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>235</v>
+      </c>
+      <c r="B47">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C47">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D47">
+        <v>0.96657080399999995</v>
+      </c>
+      <c r="E47">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>236</v>
+      </c>
+      <c r="B48">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C48">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D48">
+        <v>0.92956650399999996</v>
+      </c>
+      <c r="E48">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>237</v>
+      </c>
+      <c r="B49">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C49">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D49">
+        <v>0.63015454500000001</v>
+      </c>
+      <c r="E49">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>238</v>
+      </c>
+      <c r="B50">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C50">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D50">
+        <v>0.57584163399999999</v>
+      </c>
+      <c r="E50">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>239</v>
+      </c>
+      <c r="B51">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="C51">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D51">
+        <v>0.39252177599999999</v>
+      </c>
+      <c r="E51">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>240</v>
+      </c>
+      <c r="B52">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C52">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D52">
+        <v>0.57404902800000002</v>
+      </c>
+      <c r="E52">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>241</v>
+      </c>
+      <c r="B53">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C53">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D53">
+        <v>0.53704472800000003</v>
+      </c>
+      <c r="E53">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>242</v>
+      </c>
+      <c r="B54">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C54">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D54">
+        <v>0.23763276899999999</v>
+      </c>
+      <c r="E54">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>243</v>
+      </c>
+      <c r="B55">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C55">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D55">
+        <v>0.183319858</v>
+      </c>
+      <c r="E55">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>244</v>
+      </c>
+      <c r="B56">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C56">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D56">
+        <v>0.39072917000000001</v>
+      </c>
+      <c r="E56">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>245</v>
+      </c>
+      <c r="B57">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C57">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D57">
+        <v>0.35372487000000002</v>
+      </c>
+      <c r="E57">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>246</v>
+      </c>
+      <c r="B58">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C58">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D58">
+        <v>5.4312910999999998E-2</v>
+      </c>
+      <c r="E58">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>247</v>
+      </c>
+      <c r="B59">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C59">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D59">
+        <v>0.336416259</v>
+      </c>
+      <c r="E59">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>248</v>
+      </c>
+      <c r="B60">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C60">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D60">
+        <v>0.29941195900000001</v>
+      </c>
+      <c r="E60">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>249</v>
+      </c>
+      <c r="B61">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C61">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="D61">
+        <v>3.7004299999999997E-2</v>
+      </c>
+      <c r="E61">
+        <v>0.48049999999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>250</v>
+      </c>
+      <c r="B62">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C62">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D62">
+        <v>0.96657080399999995</v>
+      </c>
+      <c r="E62">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>251</v>
+      </c>
+      <c r="B63">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C63">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D63">
+        <v>0.92956650399999996</v>
+      </c>
+      <c r="E63">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>252</v>
+      </c>
+      <c r="B64">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C64">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D64">
+        <v>0.63015454500000001</v>
+      </c>
+      <c r="E64">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>253</v>
+      </c>
+      <c r="B65">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C65">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D65">
+        <v>0.57584163399999999</v>
+      </c>
+      <c r="E65">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>254</v>
+      </c>
+      <c r="B66">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="C66">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D66">
+        <v>0.39252177599999999</v>
+      </c>
+      <c r="E66">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>255</v>
+      </c>
+      <c r="B67">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C67">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D67">
+        <v>0.57404902800000002</v>
+      </c>
+      <c r="E67">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>256</v>
+      </c>
+      <c r="B68">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C68">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D68">
+        <v>0.53704472800000003</v>
+      </c>
+      <c r="E68">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>257</v>
+      </c>
+      <c r="B69">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C69">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D69">
+        <v>0.23763276899999999</v>
+      </c>
+      <c r="E69">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>258</v>
+      </c>
+      <c r="B70">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C70">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D70">
+        <v>0.183319858</v>
+      </c>
+      <c r="E70">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>259</v>
+      </c>
+      <c r="B71">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C71">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D71">
+        <v>0.39072917000000001</v>
+      </c>
+      <c r="E71">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>260</v>
+      </c>
+      <c r="B72">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C72">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D72">
+        <v>0.35372487000000002</v>
+      </c>
+      <c r="E72">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>261</v>
+      </c>
+      <c r="B73">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C73">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D73">
+        <v>5.4312910999999998E-2</v>
+      </c>
+      <c r="E73">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>262</v>
+      </c>
+      <c r="B74">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C74">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D74">
+        <v>0.336416259</v>
+      </c>
+      <c r="E74">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>263</v>
+      </c>
+      <c r="B75">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C75">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D75">
+        <v>0.29941195900000001</v>
+      </c>
+      <c r="E75">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>264</v>
+      </c>
+      <c r="B76">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C76">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="D76">
+        <v>3.7004299999999997E-2</v>
+      </c>
+      <c r="E76">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>265</v>
+      </c>
+      <c r="B77">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C77">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D77">
+        <v>0.96657080399999995</v>
+      </c>
+      <c r="E77">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>266</v>
+      </c>
+      <c r="B78">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C78">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D78">
+        <v>0.92956650399999996</v>
+      </c>
+      <c r="E78">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>267</v>
+      </c>
+      <c r="B79">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C79">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D79">
+        <v>0.63015454500000001</v>
+      </c>
+      <c r="E79">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>268</v>
+      </c>
+      <c r="B80">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C80">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D80">
+        <v>0.57584163399999999</v>
+      </c>
+      <c r="E80">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>269</v>
+      </c>
+      <c r="B81">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="C81">
+        <v>1.2495865E-2</v>
+      </c>
+      <c r="D81">
+        <v>0.39252177599999999</v>
+      </c>
+      <c r="E81">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>270</v>
+      </c>
+      <c r="B82">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C82">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D82">
+        <v>0.57404902800000002</v>
+      </c>
+      <c r="E82">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>271</v>
+      </c>
+      <c r="B83">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C83">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D83">
+        <v>0.53704472800000003</v>
+      </c>
+      <c r="E83">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>272</v>
+      </c>
+      <c r="B84">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C84">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D84">
+        <v>0.23763276899999999</v>
+      </c>
+      <c r="E84">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>273</v>
+      </c>
+      <c r="B85">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="C85">
+        <v>0.40501764099999998</v>
+      </c>
+      <c r="D85">
+        <v>0.183319858</v>
+      </c>
+      <c r="E85">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>274</v>
+      </c>
+      <c r="B86">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C86">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D86">
+        <v>0.39072917000000001</v>
+      </c>
+      <c r="E86">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>275</v>
+      </c>
+      <c r="B87">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C87">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D87">
+        <v>0.35372487000000002</v>
+      </c>
+      <c r="E87">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>276</v>
+      </c>
+      <c r="B88">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="C88">
+        <v>0.58833749899999999</v>
+      </c>
+      <c r="D88">
+        <v>5.4312910999999998E-2</v>
+      </c>
+      <c r="E88">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>277</v>
+      </c>
+      <c r="B89">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C89">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D89">
+        <v>0.336416259</v>
+      </c>
+      <c r="E89">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>278</v>
+      </c>
+      <c r="B90">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="C90">
+        <v>0.64265041000000001</v>
+      </c>
+      <c r="D90">
+        <v>0.29941195900000001</v>
+      </c>
+      <c r="E90">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>279</v>
+      </c>
+      <c r="B91">
+        <v>0.97906666899999995</v>
+      </c>
+      <c r="C91">
+        <v>0.94206236899999996</v>
+      </c>
+      <c r="D91">
+        <v>3.7004299999999997E-2</v>
+      </c>
+      <c r="E91">
+        <v>0.84450000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E91" xr:uid="{BCF963FB-848F-441E-8C2F-7C313605947B}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A73EE8F-669B-40F4-BD8D-1FAEC384025B}">
   <dimension ref="A1:E72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4273,7 +6109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BBBD394-06A5-4C91-A073-889ACA2920C4}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
